--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T18:16:37+00:00</t>
+    <t>2026-02-06T16:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Questionnaire.extension:itemPopulationContext</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -3809,10 +3809,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>90</v>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:04:48+00:00</t>
+    <t>2026-02-13T15:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:15:54+00:00</t>
+    <t>2026-02-13T15:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:40:14+00:00</t>
+    <t>2026-02-13T15:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>RORQuestionnaireHealthcareService</t>
+    <t>RORQuestionnaire</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:51:32+00:00</t>
+    <t>2026-02-17T13:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:15:51+00:00</t>
+    <t>2026-02-18T14:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -517,7 +517,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Questionnaire.extension:itemPopulationContext</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T14:26:16+00:00</t>
+    <t>2026-02-18T16:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T16:47:38+00:00</t>
+    <t>2026-02-19T09:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T09:13:17+00:00</t>
+    <t>2026-03-09T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
   </si>
   <si>
     <t>Modèle de saisie des Offres Opérationnelles.  
-Les questionnaires crées à partir de cette ressource sont utilisés par les établissements pour saisir leurs offres opérationnelles.</t>
+Les questionnaires créés à partir de cette ressource sont utilisés par les établissements pour saisir leurs offres opérationnelles.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:55:47+00:00</t>
+    <t>2026-03-09T14:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
